--- a/backend/data/financials_by_company/0267.HK.xlsx
+++ b/backend/data/financials_by_company/0267.HK.xlsx
@@ -657,55 +657,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1378219649.170417</v>
+        <v>-957534722.476819</v>
       </c>
       <c r="C2" t="n">
-        <v>0.187717</v>
+        <v>0.172221</v>
       </c>
       <c r="D2" t="n">
-        <v>165976000000</v>
+        <v>129391272662.6879</v>
       </c>
       <c r="E2" t="n">
-        <v>7359000000</v>
+        <v>-5550116182.742887</v>
       </c>
       <c r="F2" t="n">
-        <v>7342000000</v>
+        <v>-5559924930.046704</v>
       </c>
       <c r="G2" t="n">
-        <v>58202000000</v>
+        <v>57399154430.71738</v>
       </c>
       <c r="H2" t="n">
-        <v>27560000000</v>
+        <v>17345134815.58234</v>
       </c>
       <c r="I2" t="n">
-        <v>620388000000</v>
+        <v>485196224548.1569</v>
       </c>
       <c r="J2" t="n">
-        <v>173335000000</v>
+        <v>123841156479.945</v>
       </c>
       <c r="K2" t="n">
-        <v>145775000000</v>
+        <v>106496021664.3627</v>
       </c>
       <c r="L2" t="n">
-        <v>-11106000000</v>
+        <v>-6046275317.194277</v>
       </c>
       <c r="M2" t="n">
-        <v>13118000000</v>
+        <v>7475900236.725545</v>
       </c>
       <c r="N2" t="n">
-        <v>2235000000</v>
+        <v>1664217459.214215</v>
       </c>
       <c r="O2" t="n">
-        <v>52255219649.17042</v>
+        <v>62011353385.59109</v>
       </c>
       <c r="P2" t="n">
-        <v>58202000000</v>
+        <v>57399154430.71738</v>
       </c>
       <c r="Q2" t="n">
-        <v>818245000000</v>
+        <v>646976798203.6558</v>
       </c>
       <c r="R2" t="n">
         <v>29090000000</v>
@@ -714,141 +714,139 @@
         <v>29090000000</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>1.969923</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>1.969923</v>
       </c>
       <c r="V2" t="n">
-        <v>57218000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-984000000</v>
-      </c>
+        <v>57399154430.71738</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>58202000000</v>
+        <v>57399154430.71738</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>58202000000</v>
+        <v>57399154430.71738</v>
       </c>
       <c r="AA2" t="n">
-        <v>-49553000000</v>
+        <v>-24567642413.62595</v>
       </c>
       <c r="AB2" t="n">
-        <v>107755000000</v>
+        <v>81966796844.34334</v>
       </c>
       <c r="AC2" t="n">
-        <v>107755000000</v>
+        <v>81966796844.34334</v>
       </c>
       <c r="AD2" t="n">
-        <v>24902000000</v>
+        <v>17053324583.29379</v>
       </c>
       <c r="AE2" t="n">
-        <v>132657000000</v>
+        <v>99020121427.63713</v>
       </c>
       <c r="AF2" t="n">
-        <v>6596000000</v>
+        <v>2919737114.102738</v>
       </c>
       <c r="AG2" t="n">
-        <v>4080000000</v>
+        <v>-7195533542.95812</v>
       </c>
       <c r="AH2" t="n">
-        <v>-3793000000</v>
+        <v>-1138632082.851376</v>
       </c>
       <c r="AI2" t="n">
-        <v>-390000000</v>
+        <v>8221365031.815605</v>
       </c>
       <c r="AJ2" t="n">
-        <v>86000000</v>
+        <v>102991846.690074</v>
       </c>
       <c r="AK2" t="n">
-        <v>-11106000000</v>
+        <v>-6046275317.194277</v>
       </c>
       <c r="AL2" t="n">
-        <v>223000000</v>
+        <v>234592539.682947</v>
       </c>
       <c r="AM2" t="n">
-        <v>13118000000</v>
+        <v>7475900236.725545</v>
       </c>
       <c r="AN2" t="n">
-        <v>2235000000</v>
+        <v>1664217459.214215</v>
       </c>
       <c r="AO2" t="n">
-        <v>124393000000</v>
+        <v>92766227625.8454</v>
       </c>
       <c r="AP2" t="n">
-        <v>197857000000</v>
+        <v>161780573655.4989</v>
       </c>
       <c r="AQ2" t="n">
-        <v>197857000000</v>
+        <v>161780573655.4989</v>
       </c>
       <c r="AR2" t="n">
-        <v>322250000000</v>
+        <v>254546801281.3443</v>
       </c>
       <c r="AS2" t="n">
-        <v>620388000000</v>
+        <v>485196224548.1569</v>
       </c>
       <c r="AT2" t="n">
-        <v>942638000000</v>
+        <v>739743025829.5012</v>
       </c>
       <c r="AU2" t="n">
-        <v>942638000000</v>
+        <v>739743025829.5012</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-381775604.889404</v>
+        <v>-809565408.666688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.146106</v>
+        <v>0.168659</v>
       </c>
       <c r="D3" t="n">
-        <v>160787000000</v>
+        <v>156222000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-2587000000</v>
+        <v>-437000000</v>
       </c>
       <c r="F3" t="n">
-        <v>-2613000000</v>
+        <v>-4800000000</v>
       </c>
       <c r="G3" t="n">
-        <v>57594000000</v>
+        <v>64931000000</v>
       </c>
       <c r="H3" t="n">
-        <v>23059000000</v>
+        <v>20240000000</v>
       </c>
       <c r="I3" t="n">
-        <v>570303000000</v>
+        <v>537343000000</v>
       </c>
       <c r="J3" t="n">
-        <v>158200000000</v>
+        <v>155785000000</v>
       </c>
       <c r="K3" t="n">
-        <v>135141000000</v>
+        <v>135545000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-10340000000</v>
+        <v>-7065000000</v>
       </c>
       <c r="M3" t="n">
-        <v>11854000000</v>
+        <v>8253000000</v>
       </c>
       <c r="N3" t="n">
-        <v>1832000000</v>
+        <v>1407000000</v>
       </c>
       <c r="O3" t="n">
-        <v>59851224395.1106</v>
+        <v>73284434591.33331</v>
       </c>
       <c r="P3" t="n">
-        <v>57594000000</v>
+        <v>64931000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>761303000000</v>
+        <v>721820000000</v>
       </c>
       <c r="R3" t="n">
         <v>29090000000</v>
@@ -857,141 +855,139 @@
         <v>29090000000</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="U3" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="V3" t="n">
-        <v>57499000000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-95000000</v>
-      </c>
+        <v>64931000000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>57594000000</v>
+        <v>64931000000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>57594000000</v>
+        <v>64931000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-47680000000</v>
+        <v>-40892000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>105274000000</v>
+        <v>105823000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>105274000000</v>
+        <v>105823000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>18013000000</v>
+        <v>21469000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>123287000000</v>
+        <v>127292000000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5099000000</v>
+        <v>5116000000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-5562000000</v>
+        <v>-4606000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-74000000</v>
+        <v>-10977000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5948000000</v>
+        <v>11150000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-338000000</v>
+        <v>70000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-10340000000</v>
+        <v>-7065000000</v>
       </c>
       <c r="AL3" t="n">
-        <v>318000000</v>
+        <v>219000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>11854000000</v>
+        <v>8253000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1832000000</v>
+        <v>1407000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>121380000000</v>
+        <v>123083000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>191000000000</v>
+        <v>184477000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>191000000000</v>
+        <v>184477000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>312380000000</v>
+        <v>307560000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>570303000000</v>
+        <v>537343000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>882683000000</v>
+        <v>844903000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>882683000000</v>
+        <v>844903000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-809565408.666688</v>
+        <v>-381775604.889404</v>
       </c>
       <c r="C4" t="n">
-        <v>0.168659</v>
+        <v>0.146106</v>
       </c>
       <c r="D4" t="n">
-        <v>156222000000</v>
+        <v>160787000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-437000000</v>
+        <v>-2587000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-4800000000</v>
+        <v>-2613000000</v>
       </c>
       <c r="G4" t="n">
-        <v>64931000000</v>
+        <v>57594000000</v>
       </c>
       <c r="H4" t="n">
-        <v>20240000000</v>
+        <v>23059000000</v>
       </c>
       <c r="I4" t="n">
-        <v>537343000000</v>
+        <v>570303000000</v>
       </c>
       <c r="J4" t="n">
-        <v>155785000000</v>
+        <v>158200000000</v>
       </c>
       <c r="K4" t="n">
-        <v>135545000000</v>
+        <v>135141000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-7065000000</v>
+        <v>-10340000000</v>
       </c>
       <c r="M4" t="n">
-        <v>8253000000</v>
+        <v>11854000000</v>
       </c>
       <c r="N4" t="n">
-        <v>1407000000</v>
+        <v>1832000000</v>
       </c>
       <c r="O4" t="n">
-        <v>73284434591.33331</v>
+        <v>59851224395.1106</v>
       </c>
       <c r="P4" t="n">
-        <v>64931000000</v>
+        <v>57594000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>721820000000</v>
+        <v>761303000000</v>
       </c>
       <c r="R4" t="n">
         <v>29090000000</v>
@@ -1000,139 +996,141 @@
         <v>29090000000</v>
       </c>
       <c r="T4" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="V4" t="n">
-        <v>64931000000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>57499000000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-95000000</v>
+      </c>
       <c r="X4" t="n">
-        <v>64931000000</v>
+        <v>57594000000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>64931000000</v>
+        <v>57594000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-40892000000</v>
+        <v>-47680000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>105823000000</v>
+        <v>105274000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>105823000000</v>
+        <v>105274000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>21469000000</v>
+        <v>18013000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>127292000000</v>
+        <v>123287000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5116000000</v>
+        <v>5099000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4606000000</v>
+        <v>-5562000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-10977000000</v>
+        <v>-74000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>11150000000</v>
+        <v>5948000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>70000000</v>
+        <v>-338000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-7065000000</v>
+        <v>-10340000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>219000000</v>
+        <v>318000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>8253000000</v>
+        <v>11854000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1407000000</v>
+        <v>1832000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>123083000000</v>
+        <v>121380000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>184477000000</v>
+        <v>191000000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>184477000000</v>
+        <v>191000000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>307560000000</v>
+        <v>312380000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>537343000000</v>
+        <v>570303000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>844903000000</v>
+        <v>882683000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>844903000000</v>
+        <v>882683000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-957534722.476819</v>
+        <v>1378219649.170417</v>
       </c>
       <c r="C5" t="n">
-        <v>0.172221</v>
+        <v>0.187717</v>
       </c>
       <c r="D5" t="n">
-        <v>129391272662.6879</v>
+        <v>165976000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-5550116182.742887</v>
+        <v>7359000000</v>
       </c>
       <c r="F5" t="n">
-        <v>-5559924930.046704</v>
+        <v>7342000000</v>
       </c>
       <c r="G5" t="n">
-        <v>57399154430.71738</v>
+        <v>58202000000</v>
       </c>
       <c r="H5" t="n">
-        <v>17345134815.58234</v>
+        <v>27560000000</v>
       </c>
       <c r="I5" t="n">
-        <v>485196224548.1569</v>
+        <v>620388000000</v>
       </c>
       <c r="J5" t="n">
-        <v>123841156479.945</v>
+        <v>173335000000</v>
       </c>
       <c r="K5" t="n">
-        <v>106496021664.3627</v>
+        <v>145775000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-6046275317.194277</v>
+        <v>-11106000000</v>
       </c>
       <c r="M5" t="n">
-        <v>7475900236.725545</v>
+        <v>13118000000</v>
       </c>
       <c r="N5" t="n">
-        <v>1664217459.214215</v>
+        <v>2235000000</v>
       </c>
       <c r="O5" t="n">
-        <v>62011353385.59109</v>
+        <v>52255219649.17042</v>
       </c>
       <c r="P5" t="n">
-        <v>57399154430.71738</v>
+        <v>58202000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>646976798203.6558</v>
+        <v>818245000000</v>
       </c>
       <c r="R5" t="n">
         <v>29090000000</v>
@@ -1141,86 +1139,88 @@
         <v>29090000000</v>
       </c>
       <c r="T5" t="n">
-        <v>1.969923</v>
+        <v>1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>1.969923</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>57399154430.71738</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>57218000000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-984000000</v>
+      </c>
       <c r="X5" t="n">
-        <v>57399154430.71738</v>
+        <v>58202000000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>57399154430.71738</v>
+        <v>58202000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-24567642413.62595</v>
+        <v>-49553000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>81966796844.34334</v>
+        <v>107755000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>81966796844.34334</v>
+        <v>107755000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>17053324583.29379</v>
+        <v>24902000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>99020121427.63713</v>
+        <v>132657000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2919737114.102738</v>
+        <v>6596000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-7195533542.95812</v>
+        <v>4080000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1138632082.851376</v>
+        <v>-3793000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>8221365031.815605</v>
+        <v>-390000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>102991846.690074</v>
+        <v>86000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-6046275317.194277</v>
+        <v>-11106000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>234592539.682947</v>
+        <v>223000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7475900236.725545</v>
+        <v>13118000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1664217459.214215</v>
+        <v>2235000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>92766227625.8454</v>
+        <v>124393000000</v>
       </c>
       <c r="AP5" t="n">
-        <v>161780573655.4989</v>
+        <v>197857000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>161780573655.4989</v>
+        <v>197857000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>254546801281.3443</v>
+        <v>322250000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>485196224548.1569</v>
+        <v>620388000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>739743025829.5012</v>
+        <v>942638000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>739743025829.5012</v>
+        <v>942638000000</v>
       </c>
     </row>
   </sheetData>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
@@ -1621,38 +1621,40 @@
         <v>29090262630</v>
       </c>
       <c r="E2" t="n">
-        <v>2268688000000</v>
+        <v>843084000000</v>
       </c>
       <c r="F2" t="n">
-        <v>2557991000000</v>
+        <v>1449629000000</v>
       </c>
       <c r="G2" t="n">
-        <v>708103000000</v>
+        <v>584551000000</v>
       </c>
       <c r="H2" t="n">
-        <v>3296429000000</v>
+        <v>2049904000000</v>
       </c>
       <c r="I2" t="n">
-        <v>1483898000000</v>
+        <v>1042444000000</v>
       </c>
       <c r="J2" t="n">
-        <v>708103000000</v>
+        <v>584551000000</v>
       </c>
       <c r="K2" t="n">
-        <v>19049000000</v>
+        <v>16975000000</v>
       </c>
       <c r="L2" t="n">
-        <v>757487000000</v>
+        <v>617250000000</v>
       </c>
       <c r="M2" t="n">
-        <v>3296429000000</v>
+        <v>1860647000000</v>
       </c>
       <c r="N2" t="n">
-        <v>1423014000000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>956196000000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>338946000000</v>
+      </c>
       <c r="P2" t="n">
-        <v>757487000000</v>
+        <v>617250000000</v>
       </c>
       <c r="Q2" t="n">
         <v>307576000000</v>
@@ -1661,172 +1663,180 @@
         <v>307576000000</v>
       </c>
       <c r="S2" t="n">
-        <v>10652411000000</v>
+        <v>7787970000000</v>
       </c>
       <c r="T2" t="n">
-        <v>3962426000000</v>
+        <v>2588276000000</v>
       </c>
       <c r="U2" t="n">
-        <v>965788000000</v>
+        <v>1178357000000</v>
       </c>
       <c r="V2" t="n">
-        <v>134331000000</v>
+        <v>24563000000</v>
       </c>
       <c r="W2" t="n">
-        <v>17731000000</v>
+        <v>11839000000</v>
       </c>
       <c r="X2" t="n">
-        <v>2557991000000</v>
+        <v>1260372000000</v>
       </c>
       <c r="Y2" t="n">
-        <v>19049000000</v>
+        <v>16975000000</v>
       </c>
       <c r="Z2" t="n">
-        <v>2538942000000</v>
+        <v>1243397000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>13801000000</v>
+        <v>20361000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>6689985000000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+        <v>5199694000000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1422683199777.223</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>189257000000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>189257000000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>38548000000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>612984000000</v>
+        <v>197889000000</v>
       </c>
       <c r="AH2" t="n">
-        <v>481734000000</v>
+        <v>31574000000</v>
       </c>
       <c r="AI2" t="n">
-        <v>4639000000</v>
+        <v>211000000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20380000000</v>
+        <v>13232000000</v>
       </c>
       <c r="AK2" t="n">
-        <v>106231000000</v>
+        <v>153083000000</v>
       </c>
       <c r="AL2" t="n">
-        <v>12075425000000</v>
+        <v>8744166000000</v>
       </c>
       <c r="AM2" t="n">
-        <v>3901542000000</v>
+        <v>2502028000000</v>
       </c>
       <c r="AN2" t="n">
-        <v>55350000000</v>
+        <v>38173000000</v>
       </c>
       <c r="AO2" t="n">
-        <v>84972000000</v>
+        <v>67560000000</v>
       </c>
       <c r="AP2" t="n">
-        <v>135218000000</v>
+        <v>22858000000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3093902000000</v>
+        <v>1953255000000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1692789000000</v>
+        <v>1407747000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1401113000000</v>
+        <v>545508000000</v>
       </c>
       <c r="AT2" t="n">
-        <v>174688000000</v>
+        <v>178329000000</v>
       </c>
       <c r="AU2" t="n">
-        <v>66955000000</v>
+        <v>52189000000</v>
       </c>
       <c r="AV2" t="n">
-        <v>107733000000</v>
+        <v>126140000000</v>
       </c>
       <c r="AW2" t="n">
-        <v>40691000000</v>
+        <v>32709000000</v>
       </c>
       <c r="AX2" t="n">
-        <v>49384000000</v>
+        <v>32699000000</v>
       </c>
       <c r="AY2" t="n">
-        <v>22640000000</v>
+        <v>15047000000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26744000000</v>
+        <v>17652000000</v>
       </c>
       <c r="BA2" t="n">
-        <v>267337000000</v>
+        <v>176445000000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-158287000000</v>
+        <v>-182694000000</v>
       </c>
       <c r="BC2" t="n">
-        <v>425624000000</v>
+        <v>176445000000</v>
       </c>
       <c r="BD2" t="n">
-        <v>17661000000</v>
+        <v>27344000000</v>
       </c>
       <c r="BE2" t="n">
-        <v>58409000000</v>
+        <v>176445000000</v>
       </c>
       <c r="BF2" t="n">
-        <v>349554000000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
+        <v>324260000000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>21126000000</v>
+      </c>
       <c r="BH2" t="n">
-        <v>8173883000000</v>
+        <v>6242138000000</v>
       </c>
       <c r="BI2" t="n">
-        <v>792326000000</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>111748000000</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>123637000000</v>
+        <v>92718000000</v>
       </c>
       <c r="BL2" t="n">
-        <v>3500000000</v>
+        <v>3564000000</v>
       </c>
       <c r="BM2" t="n">
-        <v>93660000000</v>
+        <v>91232000000</v>
       </c>
       <c r="BN2" t="n">
-        <v>10868000000</v>
+        <v>10330000000</v>
       </c>
       <c r="BO2" t="n">
-        <v>15609000000</v>
+        <v>8277000000</v>
       </c>
       <c r="BP2" t="n">
-        <v>5701725000000</v>
+        <v>4761154000000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>88884000000</v>
+        <v>141482000000</v>
       </c>
       <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="n">
-        <v>1299833000000</v>
+        <v>1246784000000</v>
       </c>
       <c r="BT2" t="n">
-        <v>1029579000000</v>
+        <v>657214000000</v>
       </c>
       <c r="BU2" t="n">
-        <v>270254000000</v>
+        <v>589570000000</v>
       </c>
       <c r="BV2" t="n">
-        <v>265054000000</v>
+        <v>142061000000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5200000000</v>
+        <v>589570000000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>29090262630</v>
       </c>
@@ -1834,38 +1844,40 @@
         <v>29090262630</v>
       </c>
       <c r="E3" t="n">
-        <v>2262980000000</v>
+        <v>1725076000000</v>
       </c>
       <c r="F3" t="n">
-        <v>2495022000000</v>
+        <v>1948275000000</v>
       </c>
       <c r="G3" t="n">
-        <v>654565000000</v>
+        <v>617768000000</v>
       </c>
       <c r="H3" t="n">
-        <v>3177852000000</v>
+        <v>2588856000000</v>
       </c>
       <c r="I3" t="n">
-        <v>1595182000000</v>
+        <v>1314023000000</v>
       </c>
       <c r="J3" t="n">
-        <v>654565000000</v>
+        <v>617768000000</v>
       </c>
       <c r="K3" t="n">
-        <v>20348000000</v>
+        <v>19528000000</v>
       </c>
       <c r="L3" t="n">
-        <v>703178000000</v>
+        <v>660109000000</v>
       </c>
       <c r="M3" t="n">
-        <v>3177852000000</v>
+        <v>2469435000000</v>
       </c>
       <c r="N3" t="n">
-        <v>1336782000000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>1234677000000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>574568000000</v>
+      </c>
       <c r="P3" t="n">
-        <v>703178000000</v>
+        <v>660109000000</v>
       </c>
       <c r="Q3" t="n">
         <v>307576000000</v>
@@ -1874,178 +1886,184 @@
         <v>307576000000</v>
       </c>
       <c r="S3" t="n">
-        <v>9994138000000</v>
+        <v>9307366000000</v>
       </c>
       <c r="T3" t="n">
-        <v>3761979000000</v>
+        <v>3262649000000</v>
       </c>
       <c r="U3" t="n">
-        <v>27715000000</v>
+        <v>1122258000000</v>
       </c>
       <c r="V3" t="n">
-        <v>73755000000</v>
+        <v>72393000000</v>
       </c>
       <c r="W3" t="n">
-        <v>16747000000</v>
+        <v>18153000000</v>
       </c>
       <c r="X3" t="n">
-        <v>2495022000000</v>
+        <v>1828854000000</v>
       </c>
       <c r="Y3" t="n">
-        <v>20348000000</v>
+        <v>19528000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>2474674000000</v>
+        <v>1809326000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>16130000000</v>
+        <v>17410000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6232159000000</v>
+        <v>6044717000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>985044293584.0646</v>
+        <v>1249266452611.135</v>
       </c>
       <c r="AD3" t="n">
-        <v>301197688090.7372</v>
+        <v>119421000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>301197688090.7372</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>119421000000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>61502000000</v>
+      </c>
       <c r="AG3" t="n">
-        <v>457842000000</v>
+        <v>465715000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>328472000000</v>
+        <v>352081000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1411000000</v>
+        <v>498000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14835000000</v>
+        <v>22858000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>113124000000</v>
+        <v>90278000000</v>
       </c>
       <c r="AL3" t="n">
-        <v>11330920000000</v>
+        <v>10542043000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>3503579000000</v>
+        <v>3183303000000</v>
       </c>
       <c r="AN3" t="n">
-        <v>56324000000</v>
+        <v>39296000000</v>
       </c>
       <c r="AO3" t="n">
-        <v>83327000000</v>
+        <v>88830000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>77562000000</v>
+        <v>80867000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2770879000000</v>
+        <v>2523549000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1478764000000</v>
+        <v>1387663000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1292115000000</v>
+        <v>1135886000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>166578000000</v>
+        <v>164928000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>56787000000</v>
+        <v>60464000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>109791000000</v>
+        <v>104464000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>38153000000</v>
+        <v>35407000000</v>
       </c>
       <c r="AX3" t="n">
-        <v>48613000000</v>
+        <v>42341000000</v>
       </c>
       <c r="AY3" t="n">
-        <v>22537000000</v>
+        <v>16718000000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26076000000</v>
+        <v>25623000000</v>
       </c>
       <c r="BA3" t="n">
-        <v>262143000000</v>
+        <v>201023000000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-161525000000</v>
+        <v>-147477000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>423668000000</v>
+        <v>348500000000</v>
       </c>
       <c r="BD3" t="n">
-        <v>20046000000</v>
+        <v>19662000000</v>
       </c>
       <c r="BE3" t="n">
-        <v>62273000000</v>
+        <v>50804000000</v>
       </c>
       <c r="BF3" t="n">
-        <v>341349000000</v>
-      </c>
-      <c r="BG3" t="inlineStr"/>
+        <v>278034000000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>18725725359.95393</v>
+      </c>
       <c r="BH3" t="n">
-        <v>7827341000000</v>
+        <v>7358740000000</v>
       </c>
       <c r="BI3" t="n">
-        <v>771206000000</v>
+        <v>826355000000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>87925000000</v>
+        <v>91429000000</v>
       </c>
       <c r="BK3" t="n">
-        <v>135142000000</v>
+        <v>109050000000</v>
       </c>
       <c r="BL3" t="n">
-        <v>3402000000</v>
+        <v>3619000000</v>
       </c>
       <c r="BM3" t="n">
-        <v>103262000000</v>
+        <v>86980000000</v>
       </c>
       <c r="BN3" t="n">
-        <v>11855000000</v>
+        <v>8034000000</v>
       </c>
       <c r="BO3" t="n">
-        <v>16623000000</v>
+        <v>10417000000</v>
       </c>
       <c r="BP3" t="n">
-        <v>5492344000000</v>
+        <v>5150043000000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>92408000000</v>
+        <v>48542000000</v>
       </c>
       <c r="BR3" t="n">
-        <v>63807000000</v>
+        <v>48542000000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1199907000000</v>
+        <v>1086385000000</v>
       </c>
       <c r="BT3" t="n">
-        <v>988213000000</v>
+        <v>882714000000</v>
       </c>
       <c r="BU3" t="n">
-        <v>211694000000</v>
+        <v>203671000000</v>
       </c>
       <c r="BV3" t="n">
-        <v>207190000000</v>
+        <v>198067000000</v>
       </c>
       <c r="BW3" t="n">
-        <v>4504000000</v>
+        <v>5604000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
         <v>29090262630</v>
       </c>
@@ -2053,40 +2071,38 @@
         <v>29090262630</v>
       </c>
       <c r="E4" t="n">
-        <v>1725076000000</v>
+        <v>2262980000000</v>
       </c>
       <c r="F4" t="n">
-        <v>1948275000000</v>
+        <v>2495022000000</v>
       </c>
       <c r="G4" t="n">
-        <v>617768000000</v>
+        <v>654565000000</v>
       </c>
       <c r="H4" t="n">
-        <v>2588856000000</v>
+        <v>3177852000000</v>
       </c>
       <c r="I4" t="n">
-        <v>1314023000000</v>
+        <v>1595182000000</v>
       </c>
       <c r="J4" t="n">
-        <v>617768000000</v>
+        <v>654565000000</v>
       </c>
       <c r="K4" t="n">
-        <v>19528000000</v>
+        <v>20348000000</v>
       </c>
       <c r="L4" t="n">
-        <v>660109000000</v>
+        <v>703178000000</v>
       </c>
       <c r="M4" t="n">
-        <v>2469435000000</v>
+        <v>3177852000000</v>
       </c>
       <c r="N4" t="n">
-        <v>1234677000000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>574568000000</v>
-      </c>
+        <v>1336782000000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>660109000000</v>
+        <v>703178000000</v>
       </c>
       <c r="Q4" t="n">
         <v>307576000000</v>
@@ -2095,180 +2111,176 @@
         <v>307576000000</v>
       </c>
       <c r="S4" t="n">
-        <v>9307366000000</v>
+        <v>9994138000000</v>
       </c>
       <c r="T4" t="n">
-        <v>3262649000000</v>
+        <v>3761979000000</v>
       </c>
       <c r="U4" t="n">
-        <v>1122258000000</v>
+        <v>27715000000</v>
       </c>
       <c r="V4" t="n">
-        <v>72393000000</v>
+        <v>73755000000</v>
       </c>
       <c r="W4" t="n">
-        <v>18153000000</v>
+        <v>16747000000</v>
       </c>
       <c r="X4" t="n">
-        <v>1828854000000</v>
+        <v>2495022000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>19528000000</v>
+        <v>20348000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1809326000000</v>
+        <v>2474674000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>17410000000</v>
+        <v>16130000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6044717000000</v>
+        <v>6232159000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1249266452611.135</v>
+        <v>985044293584.0646</v>
       </c>
       <c r="AD4" t="n">
-        <v>119421000000</v>
+        <v>301197688090.7372</v>
       </c>
       <c r="AE4" t="n">
-        <v>119421000000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>61502000000</v>
-      </c>
+        <v>301197688090.7372</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>465715000000</v>
+        <v>457842000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>352081000000</v>
+        <v>328472000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>498000000</v>
+        <v>1411000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22858000000</v>
+        <v>14835000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>90278000000</v>
+        <v>113124000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>10542043000000</v>
+        <v>11330920000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3183303000000</v>
+        <v>3503579000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>39296000000</v>
+        <v>56324000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>88830000000</v>
+        <v>83327000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>80867000000</v>
+        <v>77562000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2523549000000</v>
+        <v>2770879000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>1387663000000</v>
+        <v>1478764000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1135886000000</v>
+        <v>1292115000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>164928000000</v>
+        <v>166578000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>60464000000</v>
+        <v>56787000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>104464000000</v>
+        <v>109791000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>35407000000</v>
+        <v>38153000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>42341000000</v>
+        <v>48613000000</v>
       </c>
       <c r="AY4" t="n">
-        <v>16718000000</v>
+        <v>22537000000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25623000000</v>
+        <v>26076000000</v>
       </c>
       <c r="BA4" t="n">
-        <v>201023000000</v>
+        <v>262143000000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-147477000000</v>
+        <v>-161525000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>348500000000</v>
+        <v>423668000000</v>
       </c>
       <c r="BD4" t="n">
-        <v>19662000000</v>
+        <v>20046000000</v>
       </c>
       <c r="BE4" t="n">
-        <v>50804000000</v>
+        <v>62273000000</v>
       </c>
       <c r="BF4" t="n">
-        <v>278034000000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>18725725359.95393</v>
-      </c>
+        <v>341349000000</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>7358740000000</v>
+        <v>7827341000000</v>
       </c>
       <c r="BI4" t="n">
-        <v>826355000000</v>
+        <v>771206000000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>91429000000</v>
+        <v>87925000000</v>
       </c>
       <c r="BK4" t="n">
-        <v>109050000000</v>
+        <v>135142000000</v>
       </c>
       <c r="BL4" t="n">
-        <v>3619000000</v>
+        <v>3402000000</v>
       </c>
       <c r="BM4" t="n">
-        <v>86980000000</v>
+        <v>103262000000</v>
       </c>
       <c r="BN4" t="n">
-        <v>8034000000</v>
+        <v>11855000000</v>
       </c>
       <c r="BO4" t="n">
-        <v>10417000000</v>
+        <v>16623000000</v>
       </c>
       <c r="BP4" t="n">
-        <v>5150043000000</v>
+        <v>5492344000000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>48542000000</v>
+        <v>92408000000</v>
       </c>
       <c r="BR4" t="n">
-        <v>48542000000</v>
+        <v>63807000000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1086385000000</v>
+        <v>1199907000000</v>
       </c>
       <c r="BT4" t="n">
-        <v>882714000000</v>
+        <v>988213000000</v>
       </c>
       <c r="BU4" t="n">
-        <v>203671000000</v>
+        <v>211694000000</v>
       </c>
       <c r="BV4" t="n">
-        <v>198067000000</v>
+        <v>207190000000</v>
       </c>
       <c r="BW4" t="n">
-        <v>5604000000</v>
+        <v>4504000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
@@ -2278,40 +2290,38 @@
         <v>29090262630</v>
       </c>
       <c r="E5" t="n">
-        <v>843084000000</v>
+        <v>2268688000000</v>
       </c>
       <c r="F5" t="n">
-        <v>1449629000000</v>
+        <v>2557991000000</v>
       </c>
       <c r="G5" t="n">
-        <v>584551000000</v>
+        <v>708103000000</v>
       </c>
       <c r="H5" t="n">
-        <v>2049904000000</v>
+        <v>3296429000000</v>
       </c>
       <c r="I5" t="n">
-        <v>1042444000000</v>
+        <v>1483898000000</v>
       </c>
       <c r="J5" t="n">
-        <v>584551000000</v>
+        <v>708103000000</v>
       </c>
       <c r="K5" t="n">
-        <v>16975000000</v>
+        <v>19049000000</v>
       </c>
       <c r="L5" t="n">
-        <v>617250000000</v>
+        <v>757487000000</v>
       </c>
       <c r="M5" t="n">
-        <v>1860647000000</v>
+        <v>3296429000000</v>
       </c>
       <c r="N5" t="n">
-        <v>956196000000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>338946000000</v>
-      </c>
+        <v>1423014000000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>617250000000</v>
+        <v>757487000000</v>
       </c>
       <c r="Q5" t="n">
         <v>307576000000</v>
@@ -2320,173 +2330,163 @@
         <v>307576000000</v>
       </c>
       <c r="S5" t="n">
-        <v>7787970000000</v>
+        <v>10652411000000</v>
       </c>
       <c r="T5" t="n">
-        <v>2588276000000</v>
+        <v>3962426000000</v>
       </c>
       <c r="U5" t="n">
-        <v>1178357000000</v>
+        <v>965788000000</v>
       </c>
       <c r="V5" t="n">
-        <v>24563000000</v>
+        <v>134331000000</v>
       </c>
       <c r="W5" t="n">
-        <v>11839000000</v>
+        <v>17731000000</v>
       </c>
       <c r="X5" t="n">
-        <v>1260372000000</v>
+        <v>2557991000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>16975000000</v>
+        <v>19049000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1243397000000</v>
+        <v>2538942000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>20361000000</v>
+        <v>13801000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>5199694000000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1422683199777.223</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>189257000000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>189257000000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>38548000000</v>
-      </c>
+        <v>6689985000000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>197889000000</v>
+        <v>612984000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>31574000000</v>
+        <v>481734000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>211000000</v>
+        <v>4639000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13232000000</v>
+        <v>20380000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>153083000000</v>
+        <v>106231000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>8744166000000</v>
+        <v>12075425000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>2502028000000</v>
+        <v>3901542000000</v>
       </c>
       <c r="AN5" t="n">
-        <v>38173000000</v>
+        <v>55350000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>67560000000</v>
+        <v>84972000000</v>
       </c>
       <c r="AP5" t="n">
-        <v>22858000000</v>
+        <v>135218000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1953255000000</v>
+        <v>3093902000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1407747000000</v>
+        <v>1692789000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>545508000000</v>
+        <v>1401113000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>178329000000</v>
+        <v>174688000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>52189000000</v>
+        <v>66955000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>126140000000</v>
+        <v>107733000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>32709000000</v>
+        <v>40691000000</v>
       </c>
       <c r="AX5" t="n">
-        <v>32699000000</v>
+        <v>49384000000</v>
       </c>
       <c r="AY5" t="n">
-        <v>15047000000</v>
+        <v>22640000000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17652000000</v>
+        <v>26744000000</v>
       </c>
       <c r="BA5" t="n">
-        <v>176445000000</v>
+        <v>267337000000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-182694000000</v>
+        <v>-158287000000</v>
       </c>
       <c r="BC5" t="n">
-        <v>176445000000</v>
+        <v>425624000000</v>
       </c>
       <c r="BD5" t="n">
-        <v>27344000000</v>
+        <v>17661000000</v>
       </c>
       <c r="BE5" t="n">
-        <v>176445000000</v>
+        <v>58409000000</v>
       </c>
       <c r="BF5" t="n">
-        <v>324260000000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>21126000000</v>
-      </c>
+        <v>349554000000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>6242138000000</v>
+        <v>8173883000000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>792326000000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>111748000000</v>
       </c>
       <c r="BK5" t="n">
-        <v>92718000000</v>
+        <v>123637000000</v>
       </c>
       <c r="BL5" t="n">
-        <v>3564000000</v>
+        <v>3500000000</v>
       </c>
       <c r="BM5" t="n">
-        <v>91232000000</v>
+        <v>93660000000</v>
       </c>
       <c r="BN5" t="n">
-        <v>10330000000</v>
+        <v>10868000000</v>
       </c>
       <c r="BO5" t="n">
-        <v>8277000000</v>
+        <v>15609000000</v>
       </c>
       <c r="BP5" t="n">
-        <v>4761154000000</v>
+        <v>5701725000000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>141482000000</v>
+        <v>88884000000</v>
       </c>
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>1246784000000</v>
+        <v>1299833000000</v>
       </c>
       <c r="BT5" t="n">
-        <v>657214000000</v>
+        <v>1029579000000</v>
       </c>
       <c r="BU5" t="n">
-        <v>589570000000</v>
+        <v>270254000000</v>
       </c>
       <c r="BV5" t="n">
-        <v>142061000000</v>
+        <v>265054000000</v>
       </c>
       <c r="BW5" t="n">
-        <v>589570000000</v>
+        <v>5200000000</v>
       </c>
     </row>
   </sheetData>
@@ -2732,552 +2732,552 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-94366000000</v>
+        <v>-53284384936.76633</v>
       </c>
       <c r="C2" t="n">
-        <v>-1831324000000</v>
+        <v>-840434721276.8304</v>
       </c>
       <c r="D2" t="n">
-        <v>2115232000000</v>
+        <v>1030390921562.542</v>
       </c>
       <c r="E2" t="n">
-        <v>-28647000000</v>
+        <v>-20021288038.30696</v>
       </c>
       <c r="F2" t="n">
-        <v>385399000000</v>
+        <v>295041397129.5425</v>
       </c>
       <c r="G2" t="n">
-        <v>359383000000</v>
+        <v>374346753872.1169</v>
       </c>
       <c r="H2" t="n">
-        <v>4088000000</v>
+        <v>4009325460.435031</v>
       </c>
       <c r="I2" t="n">
-        <v>21928000000</v>
+        <v>-83314682203.00946</v>
       </c>
       <c r="J2" t="n">
-        <v>193822000000</v>
+        <v>170144982918.8285</v>
       </c>
       <c r="K2" t="n">
-        <v>5038000000</v>
+        <v>40688318607.44852</v>
       </c>
       <c r="L2" t="n">
-        <v>-49169000000</v>
+        <v>-33581881185.8334</v>
       </c>
       <c r="M2" t="n">
-        <v>-15272000000</v>
+        <v>-12793058671.00279</v>
       </c>
       <c r="N2" t="n">
-        <v>-15272000000</v>
+        <v>-12793058671.00279</v>
       </c>
       <c r="O2" t="n">
-        <v>283908000000</v>
+        <v>189956200285.7121</v>
       </c>
       <c r="P2" t="n">
-        <v>283908000000</v>
+        <v>189956200285.7121</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1831324000000</v>
+        <v>-840434721276.8304</v>
       </c>
       <c r="R2" t="n">
-        <v>2115232000000</v>
+        <v>1030390921562.542</v>
       </c>
       <c r="S2" t="n">
-        <v>-106175000000</v>
+        <v>-220196568223.3786</v>
       </c>
       <c r="T2" t="n">
-        <v>5598000000</v>
+        <v>5805961008.25077</v>
       </c>
       <c r="U2" t="n">
-        <v>-90260000000</v>
+        <v>-206768393164.4537</v>
       </c>
       <c r="V2" t="n">
-        <v>3862555000000</v>
+        <v>3096970551739.792</v>
       </c>
       <c r="W2" t="n">
-        <v>-3952815000000</v>
+        <v>-3303738944904.246</v>
       </c>
       <c r="X2" t="n">
-        <v>5566000000</v>
+        <v>-1014387950.336366</v>
       </c>
       <c r="Y2" t="n">
-        <v>6417000000</v>
+        <v>1924966658.374006</v>
       </c>
       <c r="Z2" t="n">
-        <v>-851000000</v>
+        <v>-2939354608.710372</v>
       </c>
       <c r="AA2" t="n">
-        <v>-27079000000</v>
+        <v>-18219748116.83932</v>
       </c>
       <c r="AB2" t="n">
-        <v>1568000000</v>
+        <v>1801539921.467647</v>
       </c>
       <c r="AC2" t="n">
-        <v>-28647000000</v>
+        <v>-20021288038.30696</v>
       </c>
       <c r="AD2" t="n">
-        <v>-65719000000</v>
+        <v>-33263096898.45936</v>
       </c>
       <c r="AE2" t="n">
-        <v>-22113000000</v>
+        <v>-18764133592.20114</v>
       </c>
       <c r="AF2" t="n">
-        <v>-270913000000</v>
+        <v>-216652340864.2662</v>
       </c>
       <c r="AG2" t="n">
-        <v>-119092000000</v>
+        <v>21089624098.81432</v>
       </c>
       <c r="AH2" t="n">
-        <v>186428000000</v>
+        <v>145497235735.5547</v>
       </c>
       <c r="AI2" t="n">
-        <v>-12683000000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>17938564027.46324</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
       <c r="AK2" t="n">
-        <v>9423000000</v>
+        <v>-27144073372.09511</v>
       </c>
       <c r="AL2" t="n">
-        <v>-333113000000</v>
+        <v>-383926630405.5111</v>
       </c>
       <c r="AM2" t="n">
-        <v>45867000000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>31755819396.10621</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>103094000000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>27560000000</v>
+        <v>17345134815.58234</v>
       </c>
       <c r="AP2" t="n">
-        <v>4450000000</v>
+        <v>2123593791.276292</v>
       </c>
       <c r="AQ2" t="n">
-        <v>23110000000</v>
+        <v>15221541024.30605</v>
       </c>
       <c r="AR2" t="n">
-        <v>-29632000000</v>
+        <v>-16134571919.16964</v>
       </c>
       <c r="AS2" t="n">
-        <v>-3793000000</v>
+        <v>-1138632082.851376</v>
       </c>
       <c r="AT2" t="n">
-        <v>132657000000</v>
+        <v>99020121427.63713</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-47102000000</v>
+        <v>145926000000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1553791000000</v>
+        <v>-1096140000000</v>
       </c>
       <c r="D3" t="n">
-        <v>1630176000000</v>
+        <v>1080173000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-24304000000</v>
+        <v>-20267000000</v>
       </c>
       <c r="F3" t="n">
-        <v>359383000000</v>
+        <v>427809000000</v>
       </c>
       <c r="G3" t="n">
-        <v>427809000000</v>
+        <v>295821000000</v>
       </c>
       <c r="H3" t="n">
-        <v>3710000000</v>
+        <v>11254000000</v>
       </c>
       <c r="I3" t="n">
-        <v>-72136000000</v>
+        <v>120734000000</v>
       </c>
       <c r="J3" t="n">
-        <v>-11058000000</v>
+        <v>-93804000000</v>
       </c>
       <c r="K3" t="n">
-        <v>1261000000</v>
+        <v>4758000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-43735000000</v>
+        <v>-41865000000</v>
       </c>
       <c r="M3" t="n">
-        <v>-17300000000</v>
+        <v>-16404000000</v>
       </c>
       <c r="N3" t="n">
-        <v>-17300000000</v>
+        <v>-16404000000</v>
       </c>
       <c r="O3" t="n">
-        <v>76385000000</v>
+        <v>-15967000000</v>
       </c>
       <c r="P3" t="n">
-        <v>76385000000</v>
+        <v>-15967000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1553791000000</v>
+        <v>-1096140000000</v>
       </c>
       <c r="R3" t="n">
-        <v>1630176000000</v>
+        <v>1080173000000</v>
       </c>
       <c r="S3" t="n">
-        <v>-38280000000</v>
+        <v>48345000000</v>
       </c>
       <c r="T3" t="n">
-        <v>7420000000</v>
+        <v>6229000000</v>
       </c>
       <c r="U3" t="n">
-        <v>-21595000000</v>
+        <v>-98612000000</v>
       </c>
       <c r="V3" t="n">
-        <v>2807715000000</v>
+        <v>2605903000000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2829310000000</v>
+        <v>-2704515000000</v>
       </c>
       <c r="X3" t="n">
-        <v>-1428000000</v>
+        <v>159936000000</v>
       </c>
       <c r="Y3" t="n">
-        <v>2155000000</v>
+        <v>167271000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3583000000</v>
+        <v>-7335000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-22677000000</v>
+        <v>-19208000000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1627000000</v>
+        <v>1059000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-24304000000</v>
+        <v>-20267000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-22798000000</v>
+        <v>166193000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-29910000000</v>
+        <v>-28967000000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-192964000000</v>
+        <v>-26087000000</v>
       </c>
       <c r="AG3" t="n">
-        <v>223432000000</v>
+        <v>1709000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>111124000000</v>
+        <v>302174000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-25992000000</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>2662000000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>7203492596.147693</v>
+      </c>
       <c r="AK3" t="n">
-        <v>-14348000000</v>
+        <v>-7381000000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-487773000000</v>
+        <v>-322990000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>40093000000</v>
+        <v>37495000000</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>23059000000</v>
+        <v>20240000000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4097000000</v>
+        <v>2961000000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>18962000000</v>
+        <v>17279000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-47096000000</v>
+        <v>-28226000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-74000000</v>
+        <v>-10977000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>123287000000</v>
+        <v>127292000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>145926000000</v>
+        <v>-47102000000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1096140000000</v>
+        <v>-1553791000000</v>
       </c>
       <c r="D4" t="n">
-        <v>1080173000000</v>
+        <v>1630176000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-20267000000</v>
+        <v>-24304000000</v>
       </c>
       <c r="F4" t="n">
+        <v>359383000000</v>
+      </c>
+      <c r="G4" t="n">
         <v>427809000000</v>
       </c>
-      <c r="G4" t="n">
-        <v>295821000000</v>
-      </c>
       <c r="H4" t="n">
-        <v>11254000000</v>
+        <v>3710000000</v>
       </c>
       <c r="I4" t="n">
-        <v>120734000000</v>
+        <v>-72136000000</v>
       </c>
       <c r="J4" t="n">
-        <v>-93804000000</v>
+        <v>-11058000000</v>
       </c>
       <c r="K4" t="n">
-        <v>4758000000</v>
+        <v>1261000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-41865000000</v>
+        <v>-43735000000</v>
       </c>
       <c r="M4" t="n">
-        <v>-16404000000</v>
+        <v>-17300000000</v>
       </c>
       <c r="N4" t="n">
-        <v>-16404000000</v>
+        <v>-17300000000</v>
       </c>
       <c r="O4" t="n">
-        <v>-15967000000</v>
+        <v>76385000000</v>
       </c>
       <c r="P4" t="n">
-        <v>-15967000000</v>
+        <v>76385000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1096140000000</v>
+        <v>-1553791000000</v>
       </c>
       <c r="R4" t="n">
-        <v>1080173000000</v>
+        <v>1630176000000</v>
       </c>
       <c r="S4" t="n">
-        <v>48345000000</v>
+        <v>-38280000000</v>
       </c>
       <c r="T4" t="n">
-        <v>6229000000</v>
+        <v>7420000000</v>
       </c>
       <c r="U4" t="n">
-        <v>-98612000000</v>
+        <v>-21595000000</v>
       </c>
       <c r="V4" t="n">
-        <v>2605903000000</v>
+        <v>2807715000000</v>
       </c>
       <c r="W4" t="n">
-        <v>-2704515000000</v>
+        <v>-2829310000000</v>
       </c>
       <c r="X4" t="n">
-        <v>159936000000</v>
+        <v>-1428000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>167271000000</v>
+        <v>2155000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-7335000000</v>
+        <v>-3583000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-19208000000</v>
+        <v>-22677000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1059000000</v>
+        <v>1627000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-20267000000</v>
+        <v>-24304000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>166193000000</v>
+        <v>-22798000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-28967000000</v>
+        <v>-29910000000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-26087000000</v>
+        <v>-192964000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1709000000</v>
+        <v>223432000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>302174000000</v>
+        <v>111124000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2662000000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>7203492596.147693</v>
-      </c>
+        <v>-25992000000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>-7381000000</v>
+        <v>-14348000000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-322990000000</v>
+        <v>-487773000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>37495000000</v>
+        <v>40093000000</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>20240000000</v>
+        <v>23059000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2961000000</v>
+        <v>4097000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17279000000</v>
+        <v>18962000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-28226000000</v>
+        <v>-47096000000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-10977000000</v>
+        <v>-74000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>127292000000</v>
+        <v>123287000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-53284384936.76633</v>
+        <v>-94366000000</v>
       </c>
       <c r="C5" t="n">
-        <v>-840434721276.8304</v>
+        <v>-1831324000000</v>
       </c>
       <c r="D5" t="n">
-        <v>1030390921562.542</v>
+        <v>2115232000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-20021288038.30696</v>
+        <v>-28647000000</v>
       </c>
       <c r="F5" t="n">
-        <v>295041397129.5425</v>
+        <v>385399000000</v>
       </c>
       <c r="G5" t="n">
-        <v>374346753872.1169</v>
+        <v>359383000000</v>
       </c>
       <c r="H5" t="n">
-        <v>4009325460.435031</v>
+        <v>4088000000</v>
       </c>
       <c r="I5" t="n">
-        <v>-83314682203.00946</v>
+        <v>21928000000</v>
       </c>
       <c r="J5" t="n">
-        <v>170144982918.8285</v>
+        <v>193822000000</v>
       </c>
       <c r="K5" t="n">
-        <v>40688318607.44852</v>
+        <v>5038000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-33581881185.8334</v>
+        <v>-49169000000</v>
       </c>
       <c r="M5" t="n">
-        <v>-12793058671.00279</v>
+        <v>-15272000000</v>
       </c>
       <c r="N5" t="n">
-        <v>-12793058671.00279</v>
+        <v>-15272000000</v>
       </c>
       <c r="O5" t="n">
-        <v>189956200285.7121</v>
+        <v>283908000000</v>
       </c>
       <c r="P5" t="n">
-        <v>189956200285.7121</v>
+        <v>283908000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-840434721276.8304</v>
+        <v>-1831324000000</v>
       </c>
       <c r="R5" t="n">
-        <v>1030390921562.542</v>
+        <v>2115232000000</v>
       </c>
       <c r="S5" t="n">
-        <v>-220196568223.3786</v>
+        <v>-106175000000</v>
       </c>
       <c r="T5" t="n">
-        <v>5805961008.25077</v>
+        <v>5598000000</v>
       </c>
       <c r="U5" t="n">
-        <v>-206768393164.4537</v>
+        <v>-90260000000</v>
       </c>
       <c r="V5" t="n">
-        <v>3096970551739.792</v>
+        <v>3862555000000</v>
       </c>
       <c r="W5" t="n">
-        <v>-3303738944904.246</v>
+        <v>-3952815000000</v>
       </c>
       <c r="X5" t="n">
-        <v>-1014387950.336366</v>
+        <v>5566000000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1924966658.374006</v>
+        <v>6417000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2939354608.710372</v>
+        <v>-851000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-18219748116.83932</v>
+        <v>-27079000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1801539921.467647</v>
+        <v>1568000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-20021288038.30696</v>
+        <v>-28647000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-33263096898.45936</v>
+        <v>-65719000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-18764133592.20114</v>
+        <v>-22113000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-216652340864.2662</v>
+        <v>-270913000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>21089624098.81432</v>
+        <v>-119092000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>145497235735.5547</v>
+        <v>186428000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>17938564027.46324</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
+        <v>-12683000000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>-27144073372.09511</v>
+        <v>9423000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-383926630405.5111</v>
+        <v>-333113000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>31755819396.10621</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>103094000000</v>
-      </c>
+        <v>45867000000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>17345134815.58234</v>
+        <v>27560000000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2123593791.276292</v>
+        <v>4450000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15221541024.30605</v>
+        <v>23110000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-16134571919.16964</v>
+        <v>-29632000000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-1138632082.851376</v>
+        <v>-3793000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>99020121427.63713</v>
+        <v>132657000000</v>
       </c>
     </row>
   </sheetData>
@@ -3912,217 +3912,217 @@
       </c>
       <c r="DT1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FG1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="FK1" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Guohua  Xi Ph.D.', 'age': 62, 'title': 'Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1181305, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wenwu  Zhang', 'age': 52, 'title': 'President &amp; Executive Vice Chairman', 'yearBorn': 1973, 'fiscalYear': 2024, 'totalPay': 966794, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhengjun  Liu', 'age': 60, 'title': 'VP &amp; Executive Director', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 1065490, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guoquan  Wang', 'age': 53, 'title': 'VP &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 1065490, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Huijiang', 'age': 55, 'title': 'Chief Investment Officer', 'yearBorn': 1970, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Xiaoyan  Liu', 'title': 'Accounting Supervisor', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Chen Meng Holly', 'age': 58, 'title': 'Director of Group Investor Relations &amp; Corporate Communications', 'yearBorn': 1967, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wing Kay  Choy', 'age': 50, 'title': 'Group General Counsel &amp; Joint Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Youjun  Zhang', 'age': 60, 'title': 'Assistant President', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shijun  Cheng', 'age': 60, 'title': 'Chief Auditor', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Guohua  Xi Ph.D.', 'age': 62, 'title': 'Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2024, 'totalPay': 1180669, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wenwu  Zhang', 'age': 52, 'title': 'President &amp; Executive Vice Chairman', 'yearBorn': 1973, 'fiscalYear': 2024, 'totalPay': 966273, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhengjun  Liu', 'age': 60, 'title': 'VP &amp; Executive Director', 'yearBorn': 1965, 'fiscalYear': 2024, 'totalPay': 1064917, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guoquan  Wang', 'age': 53, 'title': 'VP &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 1064917, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liang  Huijiang', 'age': 55, 'title': 'Chief Investment Officer', 'yearBorn': 1970, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Xiaoyan  Liu', 'title': 'Accounting Supervisor', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Chen Meng Holly', 'age': 58, 'title': 'Director of Group Investor Relations &amp; Corporate Communications', 'yearBorn': 1967, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wing Kay  Choy', 'age': 50, 'title': 'Group General Counsel &amp; Joint Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Youjun  Zhang', 'age': 60, 'title': 'Assistant President', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shijun  Cheng', 'age': 60, 'title': 'Chief Auditor', 'yearBorn': 1965, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4226,7 +4226,7 @@
         <v>8</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1735603200</v>
@@ -4248,34 +4248,34 @@
         <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.96</v>
+        <v>12.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.77</v>
+        <v>12.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.77</v>
+        <v>11.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>13.39</v>
+        <v>12.43</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.96</v>
+        <v>12.4</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.77</v>
+        <v>12.41</v>
       </c>
       <c r="AH2" t="n">
-        <v>12.77</v>
+        <v>11.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>13.39</v>
+        <v>12.43</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.66</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.06</v>
+        <v>5.34</v>
       </c>
       <c r="AL2" t="n">
         <v>1782777600</v>
@@ -4287,34 +4287,34 @@
         <v>6.82</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.876</v>
+        <v>0.862</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.716738</v>
+        <v>5.2789702</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.289219</v>
+        <v>4.884189</v>
       </c>
       <c r="AR2" t="n">
-        <v>36972200</v>
+        <v>36069428</v>
       </c>
       <c r="AS2" t="n">
-        <v>36972200</v>
+        <v>36069428</v>
       </c>
       <c r="AT2" t="n">
-        <v>19178580</v>
+        <v>22684415</v>
       </c>
       <c r="AU2" t="n">
-        <v>23510384</v>
+        <v>37955655</v>
       </c>
       <c r="AV2" t="n">
-        <v>23510384</v>
+        <v>37955655</v>
       </c>
       <c r="AW2" t="n">
-        <v>13.31</v>
+        <v>12.28</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.29</v>
+        <v>12.3</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4323,16 +4323,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>387482288128</v>
+        <v>357810241536</v>
       </c>
       <c r="BB2" t="n">
-        <v>377009803684</v>
+        <v>360719256612</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.869999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="BD2" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="BE2" t="n">
         <v>51.7</v>
@@ -4341,19 +4341,19 @@
         <v>3.66</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.40996042</v>
+        <v>0.37856707</v>
       </c>
       <c r="BH2" t="n">
-        <v>12.732</v>
+        <v>13.1252</v>
       </c>
       <c r="BI2" t="n">
-        <v>12.1575</v>
+        <v>12.28915</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.585</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.045138888</v>
+        <v>0.04717742</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>1967275245568</v>
+        <v>1937603166208</v>
       </c>
       <c r="BO2" t="n">
         <v>0.062140003</v>
@@ -4379,16 +4379,16 @@
         <v>0.73121</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.13796</v>
+        <v>0.13832</v>
       </c>
       <c r="BT2" t="n">
         <v>29090262630</v>
       </c>
       <c r="BU2" t="n">
-        <v>31.147066</v>
+        <v>31.130537</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.4276486</v>
+        <v>0.39511043</v>
       </c>
       <c r="BW2" t="n">
         <v>1767139200</v>
@@ -4415,16 +4415,16 @@
         <v>1.76</v>
       </c>
       <c r="CE2" t="n">
-        <v>2.081</v>
+        <v>2.05</v>
       </c>
       <c r="CF2" t="n">
-        <v>6.082</v>
+        <v>5.99</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.27810645</v>
+        <v>0.097345114</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CI2" t="n">
         <v>0.385</v>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="CL2" t="n">
-        <v>13.32</v>
+        <v>12.3</v>
       </c>
       <c r="CM2" t="n">
         <v>14.8</v>
@@ -4557,156 +4557,156 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
+          <t>[{'header': 'Dividend', 'message': '0267.HK announced a cash dividend of HKD 0.385 with an ex-date of Jun. 30, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1782748800000, 'amount': '0.385'}}]</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>1782115692</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>finmb_877097</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DX2" t="n">
+      <c r="DZ2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DZ2" t="b">
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EC2" t="n">
+        <v>-0.806447</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>946949400000</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.09999943</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>11.9 - 12.43</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>CITIC</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>CITIC Limited</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
         <is>
           <t>PREPRE</t>
         </is>
       </c>
-      <c r="EB2" t="n">
-        <v>2.7777753</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="EF2" t="b">
+      <c r="EL2" t="n">
+        <v>5.117899</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.8252001</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>-0.06287143000000001</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>0.010849953</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0.0008828888</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ES2" t="b">
         <v>0</v>
       </c>
-      <c r="EG2" t="n">
-        <v>946949400000</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.35999966</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>12.77 - 13.39</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
+      <c r="ET2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="EK2" t="n">
-        <v>19178580</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>3.4499998</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.34954405</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>9.87 - 13.8</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>-0.4800005</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-0.034782644</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>27.810646</v>
-      </c>
-      <c r="ER2" t="n">
+      <c r="EU2" t="n">
+        <v>22684415</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>1.8400002</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>0.17590824</v>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>10.46 - 13.9</t>
+        </is>
+      </c>
+      <c r="EY2" t="n">
+        <v>-1.5999994</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>-0.11510788</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>9.734510999999999</v>
+      </c>
+      <c r="FB2" t="n">
         <v>1774599000</v>
       </c>
-      <c r="ES2" t="n">
+      <c r="FC2" t="n">
         <v>1774599000</v>
       </c>
-      <c r="ET2" t="n">
+      <c r="FD2" t="n">
         <v>1774599000</v>
       </c>
-      <c r="EU2" t="n">
+      <c r="FE2" t="n">
         <v>1743145200</v>
       </c>
-      <c r="EV2" t="n">
+      <c r="FF2" t="n">
         <v>1743145200</v>
       </c>
-      <c r="EW2" t="b">
+      <c r="FG2" t="b">
         <v>0</v>
       </c>
-      <c r="EX2" t="n">
+      <c r="FH2" t="n">
         <v>2.33</v>
       </c>
-      <c r="EY2" t="n">
+      <c r="FI2" t="n">
         <v>2.51833</v>
       </c>
-      <c r="EZ2" t="n">
+      <c r="FJ2" t="n">
         <v>2.40333</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>5.5423098</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>0.58799934</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>0.046182793</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1.1624994</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>0.09561994</v>
-      </c>
-      <c r="FF2" t="inlineStr">
-        <is>
-          <t>CITIC</t>
-        </is>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>CITIC Limited</t>
-        </is>
-      </c>
-      <c r="FH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FJ2" t="b">
-        <v>0</v>
       </c>
       <c r="FK2" t="inlineStr"/>
     </row>
